--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1228 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1141,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,1014 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -880,19 +880,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1227,32 +1235,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1260,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1296,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1338,32 +1354,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1371,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,33 +1415,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,7 +1545,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1593,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1704,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1815,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1926,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2727,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2838,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2949,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3060,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3171,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3393,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,7 +3504,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3591,7 +3615,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3706,7 +3730,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3764,6 +3788,688 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>5/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -1364,24 +1364,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -1473,32 +1473,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1506,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,17 +1534,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1550,13 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1664,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1839,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1950,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2061,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2172,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2283,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2394,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2513,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2616,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2735,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2957,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,7 +3068,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,7 +3179,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3282,7 +3290,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3393,7 +3401,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3512,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3615,7 +3623,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3669,7 +3677,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3738,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3845,7 +3853,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3899,7 +3907,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3968,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4075,7 +4083,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4186,7 +4194,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4240,7 +4248,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4309,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4350,12 +4358,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4424,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4460,11 +4468,237 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr"/>
-      <c r="AC35" s="2" t="inlineStr">
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>—/26</t>
         </is>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -1592,32 +1592,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1625,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,17 +1653,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1669,13 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1703,32 +1711,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1736,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,17 +1772,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1780,13 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1830,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1847,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,33 +1891,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2069,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2180,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2291,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2369,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2402,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2426,33 +2454,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -2480,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2513,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2537,33 +2573,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -2591,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2624,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2648,33 +2692,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -2702,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2735,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2759,33 +2811,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3346,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,7 +3568,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3623,7 +3679,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3677,7 +3733,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3794,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3853,7 +3909,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3907,7 +3963,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -3968,7 +4024,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4022,7 +4078,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4139,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4194,7 +4250,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4248,7 +4304,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4365,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4363,7 +4419,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4480,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4478,7 +4534,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4595,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4583,13 +4639,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4710,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4694,13 +4754,1036 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>14/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr"/>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>13/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>19/26</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,32 +3091,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3124,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3148,33 +3152,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -3202,32 +3210,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3235,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3259,17 +3271,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3279,13 +3291,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -3313,32 +3329,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3346,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,17 +3390,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3390,13 +3410,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -3424,32 +3448,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3457,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3481,33 +3509,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -3535,32 +3567,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3568,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3592,33 +3628,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3733,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -3761,32 +3801,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3794,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3818,17 +3862,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3838,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3948,7 +3992,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3963,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -3991,32 +4035,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4024,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4048,32 +4096,32 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4106,12 +4154,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -4139,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4147,10 +4195,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4250,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4304,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -4332,32 +4396,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4365,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4389,17 +4457,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4409,12 +4477,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4480,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4534,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4649,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4764,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4879,7 +4947,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>19/26</t>
         </is>
       </c>
     </row>
@@ -4940,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5051,7 +5119,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5162,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5273,7 +5341,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5384,7 +5452,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5438,7 +5506,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5567,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5553,7 +5621,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5682,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5668,7 +5736,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5797,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5783,7 +5851,693 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>7/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>15/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,22 +1549,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,18 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,13 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,13 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,13 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2484,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2952,7 +2968,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3079,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3182,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3539,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3658,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4007,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4175,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -4187,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4253,7 +4269,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4281,32 +4297,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4314,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4338,17 +4358,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4358,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4406,24 +4426,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4433,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4482,12 +4502,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4515,32 +4535,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4548,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,37 +4596,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4630,32 +4654,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4663,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4687,37 +4715,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4745,32 +4773,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4778,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4802,17 +4834,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4822,17 +4854,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4860,32 +4892,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4893,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4917,17 +4953,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4937,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4975,32 +5011,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5008,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5072,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,13 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5086,32 +5130,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5119,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5143,33 +5191,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5197,32 +5249,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5230,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5254,17 +5310,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5274,13 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5308,32 +5368,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5341,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5365,17 +5429,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5385,13 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5506,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5606,7 +5674,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5621,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5736,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5851,7 +5919,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5966,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6077,7 +6145,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6192,7 +6260,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6321,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6307,7 +6375,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6422,7 +6490,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6537,7 +6605,689 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,18 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3083,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4023,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4142,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4273,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5340,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5487,32 +5491,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5520,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,17 +5552,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5564,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5602,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5635,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,17 +5671,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5679,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5717,32 +5729,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5750,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,37 +5790,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5848,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5865,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5909,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5909,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5980,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6034,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6062,32 +6082,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6095,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6119,33 +6143,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6260,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6288,32 +6316,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6321,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6345,37 +6377,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6490,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6605,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6720,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6831,7 +6863,7 @@
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6946,7 +6978,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7061,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7172,7 +7204,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7265,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7277,17 +7309,588 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>19/28</t>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6201,32 +6201,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6234,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,17 +6262,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6278,12 +6282,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6326,24 +6330,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6353,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6402,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6435,32 +6439,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6468,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,17 +6500,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6512,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6550,32 +6558,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6583,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,37 +6619,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,12 +6792,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6813,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6821,10 +6833,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 23分钟参与校验</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -6924,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6963,7 +6991,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7039,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7265,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7380,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7721,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7770,12 +7798,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7864,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7894,6 +7922,466 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6568,24 +6568,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6677,32 +6677,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6710,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,17 +6738,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6754,17 +6758,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6801,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6825,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6919,32 +6923,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6952,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,17 +6984,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6996,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7182,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,7 +7229,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7293,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7519,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,7 +7642,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7696,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7757,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7803,7 +7811,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7979,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8028,12 +8036,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8209,7 +8217,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8253,17 +8261,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8378,7 +8386,118 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>148.5</t>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>148.5</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6687,24 +6687,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7042,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7075,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7099,17 +7103,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7119,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7157,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7190,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7214,17 +7222,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7234,13 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7268,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7301,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7325,17 +7341,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7345,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7383,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7416,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7460,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7460,13 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7494,32 +7518,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7527,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7551,17 +7579,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7571,17 +7599,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7609,32 +7637,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7642,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7666,17 +7698,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7686,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7811,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7926,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7987,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8041,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8156,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8271,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8386,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8491,13 +8523,580 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr"/>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>—/29</t>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,14 +3425,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>142.0</t>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,14 +3663,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,17 +4017,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7290,24 +7290,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7409,24 +7409,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7528,24 +7528,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7647,24 +7647,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7756,32 +7756,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7789,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7817,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7833,17 +7837,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7871,32 +7875,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7904,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,17 +7936,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7948,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7986,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8019,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,17 +8055,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8063,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8101,32 +8113,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8134,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,17 +8174,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8178,17 +8194,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8364,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8479,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8594,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8705,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8759,7 +8775,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8931,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8989,22 +9005,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9037,12 +9053,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9081,7 +9097,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9091,12 +9107,1047 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>131.0</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
+      <c r="AC74" s="2" t="inlineStr">
         <is>
           <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8004,24 +8004,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8123,24 +8123,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8232,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8265,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8293,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8309,12 +8313,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8347,32 +8351,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8380,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8404,37 +8412,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,12 +8585,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8610,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8618,10 +8626,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
-      <c r="S69" s="2" t="inlineStr"/>
-      <c r="T69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8721,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8947,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9058,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9173,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9288,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9403,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9518,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9633,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9748,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9863,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9978,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10093,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10151,6 +10175,926 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,14 +2842,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,18 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3202,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,12 +3429,12 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3559,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,14 +5928,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -5939,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6768,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7241,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7609,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8204,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8442,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8470,32 +8474,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8503,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,37 +8535,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8598,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq57，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8618,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8745,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8784,7 +8792,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8799,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8938,32 +8946,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8971,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,33 +9007,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9049,32 +9065,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9082,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,27 +9126,27 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9164,32 +9184,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9197,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9221,17 +9245,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9241,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9303,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9312,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,17 +9364,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9356,17 +9384,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9481,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9581,7 +9609,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9596,7 +9624,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9696,7 +9724,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9711,7 +9739,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9826,7 +9854,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9941,7 +9969,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10056,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,7 +10199,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10260,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10286,7 +10314,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10401,7 +10429,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10516,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10631,7 +10659,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10746,7 +10774,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10861,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10950,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10976,7 +11004,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11065,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11091,7 +11119,812 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1311,22 +1311,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>139.3</t>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,22 +3667,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,14 +5809,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>139.3</t>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,22 +7479,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,14 +7717,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>139.3</t>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9313,24 +9313,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9379,22 +9379,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9537,32 +9537,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9570,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9598,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9614,17 +9618,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9652,32 +9656,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9685,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,17 +9717,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9729,17 +9737,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9767,32 +9775,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -9800,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9824,37 +9836,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9882,32 +9894,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9915,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9939,37 +9955,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9997,32 +10013,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10030,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10054,17 +10074,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10074,12 +10094,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10112,32 +10132,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10145,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10169,37 +10193,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10314,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10342,32 +10366,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10375,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10399,17 +10427,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10419,12 +10447,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10490,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10605,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10774,7 +10802,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10835,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10889,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11004,7 +11032,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11119,7 +11147,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11234,7 +11262,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11323,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11410,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11464,7 +11492,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11553,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11579,7 +11607,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11755,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11799,17 +11827,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11898,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11914,17 +11942,822 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>132.5</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
-        <is>
-          <t>10/30</t>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10251,32 +10251,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10284,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,17 +10312,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10328,17 +10332,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10518,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10557,7 +10561,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10633,7 +10637,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10748,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10863,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10978,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11093,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11208,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11262,7 +11266,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11327,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11362,7 +11366,7 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11377,7 +11381,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11442,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11553,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11668,7 +11672,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11783,7 +11787,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11898,7 +11902,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12013,7 +12017,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12128,7 +12132,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12182,7 +12186,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12247,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12297,7 +12301,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12362,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12473,7 +12477,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12588,7 +12592,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12703,7 +12707,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12761,6 +12765,236 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,17 +7127,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10489,32 +10489,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10522,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10546,17 +10550,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10566,17 +10570,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10604,32 +10608,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10637,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10661,17 +10669,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10681,17 +10689,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10719,32 +10727,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10752,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10776,17 +10788,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10796,17 +10808,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10834,32 +10846,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10867,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10891,17 +10907,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10911,17 +10927,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -10949,32 +10965,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10982,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11006,17 +11026,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11026,17 +11046,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11064,32 +11084,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11097,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11121,17 +11145,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11141,17 +11165,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11290,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11381,7 +11405,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11557,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11672,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11726,7 +11750,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11841,7 +11865,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12017,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12071,7 +12095,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12186,7 +12210,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12271,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12301,7 +12325,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12386,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12477,7 +12501,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12592,7 +12616,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12646,7 +12670,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12707,7 +12731,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12822,7 +12846,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12866,17 +12890,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12937,7 +12961,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12991,7 +13015,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8797,17 +8797,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9027,17 +9027,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9265,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9499,17 +9499,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9618,17 +9618,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11094,24 +11094,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11318,32 +11318,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11351,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11375,17 +11379,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11395,17 +11399,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11433,32 +11437,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11466,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11490,17 +11498,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11510,17 +11518,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11548,32 +11556,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11581,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11605,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11625,17 +11637,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11663,32 +11675,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11696,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11720,17 +11736,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11740,17 +11756,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11778,12 +11794,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11811,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11819,10 +11835,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 13分钟参与校验</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11865,7 +11897,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11893,32 +11925,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11926,7 +11962,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11950,17 +11986,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11970,17 +12006,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12044,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12041,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12065,17 +12105,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12085,17 +12125,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12196,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12238,12 +12278,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12271,7 +12311,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12279,10 +12319,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12325,7 +12381,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12440,7 +12496,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12468,32 +12524,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12501,7 +12561,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12525,17 +12585,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12545,17 +12605,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12676,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12670,7 +12730,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12791,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12785,7 +12845,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12906,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12900,7 +12960,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12961,7 +13021,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13005,17 +13065,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东35路.xlsx
+++ b/data/export/2026-10-14-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9856,17 +9856,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10213,17 +10213,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10570,17 +10570,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -12409,32 +12409,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12442,7 +12446,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12466,17 +12470,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12486,17 +12490,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12534,24 +12538,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12561,7 +12565,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12610,12 +12614,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12643,32 +12647,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12676,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12700,17 +12708,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12720,17 +12728,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12758,32 +12766,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12791,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12815,17 +12827,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12835,17 +12847,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12873,32 +12885,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12906,7 +12922,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12930,17 +12946,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12950,17 +12966,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -13021,7 +13037,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
